--- a/欢乐牧场模板.xlsx
+++ b/欢乐牧场模板.xlsx
@@ -1944,7 +1944,9 @@
   <cols>
     <col min="1" max="1" width="9" style="1"/>
     <col min="2" max="2" width="39.25" style="1" customWidth="1"/>
-    <col min="3" max="16384" width="9" style="1"/>
+    <col min="3" max="10" width="9" style="1"/>
+    <col min="11" max="11" width="12.8173076923077" style="1" customWidth="1"/>
+    <col min="12" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="41" spans="1:11">
@@ -1994,9 +1996,12 @@
       <c r="E2" s="1" t="s">
         <v>10</v>
       </c>
+      <c r="F2" s="1">
+        <v>1</v>
+      </c>
       <c r="K2" s="1">
         <f>D2-F2-G2-H2</f>
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -2015,9 +2020,12 @@
       <c r="E3" s="1" t="s">
         <v>10</v>
       </c>
+      <c r="G3" s="1">
+        <v>2</v>
+      </c>
       <c r="K3" s="1">
         <f t="shared" ref="K3:K34" si="0">D3-F3-G3-H3</f>
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -2078,9 +2086,12 @@
       <c r="E6" s="1" t="s">
         <v>15</v>
       </c>
+      <c r="F6" s="1">
+        <v>1</v>
+      </c>
       <c r="K6" s="1">
         <f t="shared" si="0"/>
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -2141,9 +2152,12 @@
       <c r="E9" s="1" t="s">
         <v>15</v>
       </c>
+      <c r="H9" s="1">
+        <v>2</v>
+      </c>
       <c r="K9" s="1">
         <f t="shared" si="0"/>
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -2288,9 +2302,12 @@
       <c r="E16" s="1" t="s">
         <v>15</v>
       </c>
+      <c r="F16" s="1">
+        <v>1</v>
+      </c>
       <c r="K16" s="1">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="17" spans="1:11">
